--- a/data/trans_orig/IP1021_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1021_2023-Provincia-trans_orig.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72358</t>
+          <t>72476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146215</t>
+          <t>144773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119185</t>
+          <t>119205</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126186</t>
+          <t>126098</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120804</t>
+          <t>120726</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>244490</t>
+          <t>244037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>252682</t>
+          <t>252707</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>532</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53473</t>
+          <t>53197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57726</t>
+          <t>57736</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60252</t>
+          <t>61088</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66386</t>
+          <t>66490</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116412</t>
+          <t>116860</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123563</t>
+          <t>123545</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>454</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30825</t>
+          <t>31332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37590</t>
+          <t>36951</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70328</t>
+          <t>70218</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74241</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>359</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41539</t>
+          <t>41493</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54154</t>
+          <t>54376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97346</t>
+          <t>97699</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101979</t>
+          <t>101994</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1677</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113671</t>
+          <t>114139</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121782</t>
+          <t>121441</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>145186</t>
+          <t>144958</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154335</t>
+          <t>154301</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>263839</t>
+          <t>262436</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274196</t>
+          <t>274796</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>129906</t>
+          <t>129624</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>152468</t>
+          <t>151480</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>283745</t>
+          <t>283583</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18255</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35664</t>
+          <t>35836</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>645104</t>
+          <t>645943</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>656880</t>
+          <t>656806</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>740350</t>
+          <t>740660</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>754323</t>
+          <t>754091</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1391112</t>
+          <t>1390940</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1408521</t>
+          <t>1409245</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1021_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1021_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4562</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6890</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5914</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7875</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>63039</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59583</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>56481</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>78081</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>72476</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>79366</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>197</t>
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>151363</t>
+          <t>119520</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144773</t>
+          <t>114712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7087</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2761</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7634</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>809</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10398</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>113883</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>108748</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>124078</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>119205</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>126098</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>125474</t>
+          <t>97741</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120726</t>
+          <t>93047</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>99741</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>249552</t>
+          <t>211624</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>244037</t>
+          <t>206256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>252707</t>
+          <t>214541</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>126839</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>216385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2221</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1808</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5071</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57156</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54026</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>58807</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>56460</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>53197</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>57736</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,9%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64470</t>
+          <t>54815</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61088</t>
+          <t>51853</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66490</t>
+          <t>56077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>120930</t>
+          <t>111971</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116860</t>
+          <t>107163</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123545</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1862,74 +1862,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>70844</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>78134</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>162</t>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2778</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3181</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3232</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,27 +2167,27 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>38393</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>36245</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>39023</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>33491</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>31332</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>34509</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>32082</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35608</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>96,91%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>90,1%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>39557</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>36951</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>40183</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>91,96%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>135</t>
@@ -2280,22 +2280,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>73049</t>
+          <t>72902</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70218</t>
+          <t>70150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74243</t>
+          <t>74141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39023</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39023</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39023</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74697</t>
+          <t>74631</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74697</t>
+          <t>74631</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74697</t>
+          <t>74631</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4674</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4145</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>10,12%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1633</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>505</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -2548,74 +2548,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>48694</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>47323</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>44872</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>41493</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>97,19%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>89,88%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>44381</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>41621</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>45766</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>90,94%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>55828</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>54376</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>56186</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>169</t>
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>100700</t>
+          <t>93075</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97699</t>
+          <t>89577</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101994</t>
+          <t>94203</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9013</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6,38%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5812</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3067</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10369</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>137212</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>132355</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>139988</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>97,06%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>93,62%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>118696</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>114139</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>121441</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>95,33%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>151221</t>
+          <t>116673</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>144958</t>
+          <t>112049</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>154301</t>
+          <t>119724</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>269917</t>
+          <t>253885</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>262436</t>
+          <t>247058</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274796</t>
+          <t>258209</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>141368</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>141368</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>141368</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>156012</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>156012</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156012</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>280520</t>
+          <t>263897</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>280520</t>
+          <t>263897</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>280520</t>
+          <t>263897</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>950</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>344</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -3234,74 +3234,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>158471</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>153985</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>131234</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>129624</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>98,48%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>140153</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>138594</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>140497</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>155927</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>151480</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>156795</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>397</t>
@@ -3309,17 +3309,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>287160</t>
+          <t>298624</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>283583</t>
+          <t>294936</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>11263</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>19304</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>13084</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>8534</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>19397</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>20185</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>24500</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17531</t>
+          <t>17123</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>35836</t>
+          <t>33763</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>689010</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>680969</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>693607</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>920</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>652256</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>645943</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>656806</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>748693</t>
+          <t>615597</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>740660</t>
+          <t>608648</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>754091</t>
+          <t>620382</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1400949</t>
+          <t>1304606</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1390940</t>
+          <t>1295343</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1409245</t>
+          <t>1311983</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>700273</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>700273</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>700273</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1426776</t>
+          <t>1329106</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1426776</t>
+          <t>1329106</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1426776</t>
+          <t>1329106</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
